--- a/groupes_reformate.xlsx
+++ b/groupes_reformate.xlsx
@@ -8,15 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xavii\Documents\badminton-summer-camp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0ED6159-1274-4325-8C7A-C0E3AA791A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55337854-A601-4F2C-A4DC-F0917C0A8D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15634" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12257" yWindow="0" windowWidth="12514" windowHeight="15514" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Avancé" sheetId="1" r:id="rId1"/>
     <sheet name="Intermédiaire" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -107,9 +120,6 @@
     <t>puce54@hotmail.com</t>
   </si>
   <si>
-    <t>Thomas Lussier***</t>
-  </si>
-  <si>
     <t>Daniel Chen</t>
   </si>
   <si>
@@ -387,6 +397,9 @@
   </si>
   <si>
     <t>nightstar.wei@gmail.com</t>
+  </si>
+  <si>
+    <t>Thomas Lussier</t>
   </si>
 </sst>
 </file>
@@ -648,43 +661,43 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1015,76 +1028,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:20" ht="22.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="14">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="25">
         <f>COUNTA(A8:A31)</f>
         <v>16</v>
       </c>
-      <c r="G2" s="15"/>
-      <c r="H2" s="16"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="19"/>
     </row>
     <row r="3" spans="1:20" ht="22.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="14">
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="25">
         <f>COUNTA(F8:F31)</f>
         <v>12</v>
       </c>
-      <c r="G3" s="15"/>
-      <c r="H3" s="16"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="19"/>
     </row>
     <row r="4" spans="1:20" ht="22.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="21">
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="28">
         <f>COUNTA(L8:L31)</f>
         <v>14</v>
       </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="16"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="19"/>
     </row>
     <row r="5" spans="1:20" ht="22.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="21">
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="28">
         <f>COUNTA(Q8:Q31)</f>
         <v>12</v>
       </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="16"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:20" ht="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="7" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.4">
@@ -1318,7 +1331,7 @@
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>27</v>
@@ -1326,115 +1339,115 @@
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
       <c r="L13" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M13" s="9" t="s">
         <v>29</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>30</v>
       </c>
       <c r="N13" s="9"/>
       <c r="O13" s="9"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="R13" s="9" t="s">
         <v>29</v>
-      </c>
-      <c r="R13" s="9" t="s">
-        <v>30</v>
       </c>
       <c r="S13" s="9"/>
       <c r="T13" s="9"/>
     </row>
     <row r="14" spans="1:20" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>31</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>32</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="F14" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="9" t="s">
         <v>31</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>32</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
       <c r="L14" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="M14" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="M14" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="N14" s="9"/>
       <c r="O14" s="9"/>
       <c r="P14" s="9"/>
       <c r="Q14" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="R14" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="R14" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="S14" s="9"/>
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:20" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>36</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="F15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>36</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
       <c r="L15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="M15" s="9" t="s">
         <v>37</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>38</v>
       </c>
       <c r="N15" s="9"/>
       <c r="O15" s="9"/>
       <c r="P15" s="9"/>
       <c r="Q15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="R15" s="9" t="s">
         <v>37</v>
-      </c>
-      <c r="R15" s="9" t="s">
-        <v>38</v>
       </c>
       <c r="S15" s="9"/>
       <c r="T15" s="9"/>
     </row>
     <row r="16" spans="1:20" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>39</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>40</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="F16" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="9" t="s">
         <v>39</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>40</v>
       </c>
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
       <c r="L16" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="M16" s="10" t="s">
         <v>41</v>
-      </c>
-      <c r="M16" s="10" t="s">
-        <v>42</v>
       </c>
       <c r="N16" s="10"/>
       <c r="O16" s="10"/>
@@ -1445,67 +1458,67 @@
       <c r="T16" s="10"/>
     </row>
     <row r="17" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="F17" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="L17" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="F17" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="L17" s="9" t="s">
+      <c r="M17" s="9" t="s">
         <v>45</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>46</v>
       </c>
       <c r="N17" s="9"/>
       <c r="O17" s="9"/>
       <c r="P17" s="9"/>
       <c r="Q17" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="R17" s="9" t="s">
         <v>45</v>
-      </c>
-      <c r="R17" s="9" t="s">
-        <v>46</v>
       </c>
       <c r="S17" s="9"/>
       <c r="T17" s="9"/>
     </row>
     <row r="18" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="L18" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="L18" s="10" t="s">
+      <c r="M18" s="10" t="s">
         <v>48</v>
-      </c>
-      <c r="M18" s="10" t="s">
-        <v>49</v>
       </c>
       <c r="N18" s="10"/>
       <c r="O18" s="10"/>
       <c r="P18" s="10"/>
       <c r="Q18" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R18" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="S18" s="10"/>
       <c r="T18" s="10"/>
@@ -1513,89 +1526,89 @@
     </row>
     <row r="19" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>50</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>51</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="F19" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" s="9" t="s">
         <v>50</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>51</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
       <c r="L19" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="M19" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="M19" s="10" t="s">
-        <v>53</v>
       </c>
       <c r="N19" s="10"/>
       <c r="O19" s="10"/>
       <c r="P19" s="10"/>
       <c r="Q19" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="R19" s="10" t="s">
         <v>120</v>
-      </c>
-      <c r="R19" s="10" t="s">
-        <v>121</v>
       </c>
       <c r="S19" s="10"/>
       <c r="T19" s="10"/>
       <c r="U19" s="11"/>
     </row>
     <row r="20" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="L20" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="L20" s="9" t="s">
+      <c r="M20" s="9" t="s">
         <v>56</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>57</v>
       </c>
       <c r="N20" s="9"/>
       <c r="O20" s="9"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R20" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S20" s="9"/>
       <c r="T20" s="9"/>
     </row>
     <row r="21" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="L21" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="L21" s="10" t="s">
+      <c r="M21" s="10" t="s">
         <v>61</v>
-      </c>
-      <c r="M21" s="10" t="s">
-        <v>62</v>
       </c>
       <c r="N21" s="10"/>
       <c r="O21" s="10"/>
@@ -1606,41 +1619,41 @@
       <c r="T21" s="10"/>
     </row>
     <row r="22" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
       <c r="L22" s="10"/>
       <c r="M22" s="10"/>
       <c r="N22" s="10"/>
       <c r="O22" s="10"/>
       <c r="P22" s="10"/>
       <c r="Q22" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R22" s="10" t="s">
         <v>65</v>
-      </c>
-      <c r="R22" s="10" t="s">
-        <v>66</v>
       </c>
       <c r="S22" s="10"/>
       <c r="T22" s="10"/>
     </row>
     <row r="23" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="26"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
@@ -1653,19 +1666,19 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A24" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>117</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>118</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>117</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>118</v>
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
@@ -1709,81 +1722,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:20" ht="22.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="22">
+      <c r="A2" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="17">
         <f>COUNTA(A8:A31)</f>
         <v>10</v>
       </c>
-      <c r="G2" s="15"/>
-      <c r="H2" s="16"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="19"/>
     </row>
     <row r="3" spans="1:20" ht="22.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="22">
+      <c r="A3" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="17">
         <f>COUNTA(F8:F31)</f>
         <v>5</v>
       </c>
-      <c r="G3" s="15"/>
-      <c r="H3" s="16"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="19"/>
     </row>
     <row r="4" spans="1:20" ht="22.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="25">
+      <c r="A4" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="24">
         <f>COUNTA(L8:L31)</f>
         <v>13</v>
       </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="16"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="19"/>
     </row>
     <row r="5" spans="1:20" ht="22.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="25">
+      <c r="A5" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="24">
         <f>COUNTA(Q8:Q31)</f>
         <v>8</v>
       </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="16"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:20" ht="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="7" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>3</v>
@@ -1795,7 +1808,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>3</v>
@@ -1807,7 +1820,7 @@
         <v>5</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M7" s="5" t="s">
         <v>3</v>
@@ -1819,7 +1832,7 @@
         <v>5</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R7" s="5" t="s">
         <v>3</v>
@@ -1832,24 +1845,24 @@
       </c>
     </row>
     <row r="8" spans="1:20" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="L8" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="L8" s="10" t="s">
+      <c r="M8" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="M8" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="N8" s="10"/>
       <c r="O8" s="10"/>
@@ -1860,56 +1873,56 @@
       <c r="T8" s="10"/>
     </row>
     <row r="9" spans="1:20" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="26"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
       <c r="L9" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="M9" s="9" t="s">
         <v>79</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>80</v>
       </c>
       <c r="N9" s="9"/>
       <c r="O9" s="9"/>
       <c r="P9" s="9"/>
       <c r="Q9" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="R9" s="9" t="s">
         <v>79</v>
-      </c>
-      <c r="R9" s="9" t="s">
-        <v>80</v>
       </c>
       <c r="S9" s="9"/>
       <c r="T9" s="9"/>
     </row>
     <row r="10" spans="1:20" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>81</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>82</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="8"/>
       <c r="F10" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" s="9" t="s">
         <v>81</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>82</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
       <c r="L10" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="10" t="s">
         <v>83</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>84</v>
       </c>
       <c r="N10" s="10"/>
       <c r="O10" s="10"/>
@@ -1921,27 +1934,27 @@
     </row>
     <row r="11" spans="1:20" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>85</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>86</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="8"/>
       <c r="F11" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" s="9" t="s">
         <v>85</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>86</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="L11" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="M11" s="10" t="s">
         <v>87</v>
-      </c>
-      <c r="M11" s="10" t="s">
-        <v>88</v>
       </c>
       <c r="N11" s="10"/>
       <c r="O11" s="10"/>
@@ -1953,163 +1966,163 @@
     </row>
     <row r="12" spans="1:20" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="8"/>
       <c r="F12" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G12" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="L12" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M12" s="9" t="s">
         <v>91</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>92</v>
       </c>
       <c r="N12" s="9"/>
       <c r="O12" s="9"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="R12" s="9" t="s">
         <v>91</v>
-      </c>
-      <c r="R12" s="9" t="s">
-        <v>92</v>
       </c>
       <c r="S12" s="9"/>
       <c r="T12" s="9"/>
     </row>
     <row r="13" spans="1:20" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>93</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>94</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="8"/>
       <c r="F13" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" s="9" t="s">
         <v>93</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>94</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
       <c r="L13" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="M13" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>96</v>
       </c>
       <c r="N13" s="9"/>
       <c r="O13" s="9"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="R13" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="R13" s="9" t="s">
-        <v>96</v>
       </c>
       <c r="S13" s="9"/>
       <c r="T13" s="9"/>
     </row>
     <row r="14" spans="1:20" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="L14" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="L14" s="9" t="s">
+      <c r="M14" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="M14" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="N14" s="9"/>
       <c r="O14" s="9"/>
       <c r="P14" s="9"/>
       <c r="Q14" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="R14" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="R14" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="S14" s="9"/>
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:20" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>101</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>102</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="8"/>
       <c r="F15" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G15" s="9" t="s">
         <v>101</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>102</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
       <c r="L15" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N15" s="9"/>
       <c r="O15" s="9"/>
       <c r="P15" s="9"/>
       <c r="Q15" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R15" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S15" s="9"/>
       <c r="T15" s="9"/>
     </row>
     <row r="16" spans="1:20" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="L16" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="L16" s="10" t="s">
+      <c r="M16" s="10" t="s">
         <v>106</v>
-      </c>
-      <c r="M16" s="10" t="s">
-        <v>107</v>
       </c>
       <c r="N16" s="10"/>
       <c r="O16" s="10"/>
@@ -2120,24 +2133,24 @@
       <c r="T16" s="10"/>
     </row>
     <row r="17" spans="1:20" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="L17" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="L17" s="10" t="s">
-        <v>110</v>
-      </c>
       <c r="M17" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N17" s="10"/>
       <c r="O17" s="10"/>
@@ -2148,33 +2161,33 @@
       <c r="T17" s="10"/>
     </row>
     <row r="18" spans="1:20" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
       <c r="L18" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="M18" s="9" t="s">
         <v>111</v>
-      </c>
-      <c r="M18" s="9" t="s">
-        <v>112</v>
       </c>
       <c r="N18" s="9"/>
       <c r="O18" s="9"/>
       <c r="P18" s="9"/>
       <c r="Q18" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="R18" s="9" t="s">
         <v>111</v>
-      </c>
-      <c r="R18" s="9" t="s">
-        <v>112</v>
       </c>
       <c r="S18" s="9"/>
       <c r="T18" s="9"/>
@@ -2182,38 +2195,38 @@
     <row r="19" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A19" s="6"/>
       <c r="L19" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="M19" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>116</v>
       </c>
       <c r="N19" s="8"/>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
       <c r="Q19" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="R19" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="R19" s="7" t="s">
-        <v>116</v>
       </c>
       <c r="S19" s="8"/>
       <c r="T19" s="8"/>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.4">
       <c r="L20" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="M20" s="9" t="s">
         <v>77</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="N20" s="9"/>
       <c r="O20" s="9"/>
       <c r="P20" s="8"/>
       <c r="Q20" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="R20" s="9" t="s">
         <v>77</v>
-      </c>
-      <c r="R20" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="S20" s="9"/>
       <c r="T20" s="9"/>
